--- a/p5 - matrizLeds/datasheet.xlsx
+++ b/p5 - matrizLeds/datasheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://correoipn-my.sharepoint.com/personal/aguevarab1900_alumno_ipn_mx/Documents/Documents/Escuela/Sistemas en Chip/sistemasChips/p5 - matrizLeds/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="11_AD4D2F04E46CFB4ACB3E20E51517CCD0683EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CE698F3-6B8A-42FB-A96C-6DCAF3828788}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="11_AD4D2F04E46CFB4ACB3E20E51517CCD0683EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12B2A1FC-A4A2-421A-B4DC-392E6EF37BF1}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
     <t>x</t>
   </si>
   <si>
-    <t>Anodo Comun</t>
+    <t>Catodo Comun</t>
   </si>
 </sst>
 </file>
